--- a/Accelerator TestCases.reconstructed.xlsx
+++ b/Accelerator TestCases.reconstructed.xlsx
@@ -2039,7 +2039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/Users/ankares/Desktop/accelerator-php/docs/Accelerator-TestEvidence-Submission/manifests/workbook-snapshot-20260803-2002.xlsx</t>
+          <t>manifests/workbook-snapshot-20260803-2002.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2079,12 +2079,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/ankares/Desktop/accelerator-php/Accelerator TestCases.xlsx</t>
+          <t>Accelerator TestCases.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6c2b4934f05818fe4ee0971ab0c8f8db2be257f2d1a1c2673813165941ea268e</t>
+          <t>8b7e9aa4f91ed00c755a62057e80d6605da2b595634d654491f389d8a7f991fa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-06T08:28:00Z</t>
+          <t>2026-08-06T14:59:37Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -19752,7 +19752,7 @@
       <c r="AC50" s="54" t="n"/>
       <c r="AD50" s="54" t="inlineStr">
         <is>
-          <t>Nothing in the exercised layer completed tasks, promoted memory, or edited Git-tracked files. Final zone confirmation: git -C /home/aliaksei/Desktop/AI-Infrastructure status --porcelain is EMPTY after all 14 cases (HEAD 3a02537 untouched); all mutations happened in the scratchpad temp copy exec-brain/ with its own git history, evidence logs in scratchpad/evidence/TC-0NN.log.</t>
+          <t>Nothing in the exercised layer completed tasks, promoted memory, or edited Git-tracked files. Final zone confirmation: git -C {repository} status --porcelain is EMPTY after all 14 cases (HEAD 3a02537 untouched); all mutations happened in the scratchpad temp copy exec-brain/ with its own git history, evidence logs in scratchpad/evidence/TC-0NN.log.</t>
         </is>
       </c>
     </row>
